--- a/backend/sample/report.xlsx
+++ b/backend/sample/report.xlsx
@@ -4,8 +4,8 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Xulosa" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Taqqoslash" state="visible" r:id="rId5"/>
+    <sheet sheetId="1" name="Taqqoslash jadvali" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Tahlil xulosasi" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Topilmadi" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
@@ -13,9 +13,90 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
-  <si>
-    <t>PricePill — Tahlil xulosasi</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
+  <si>
+    <t>№</t>
+  </si>
+  <si>
+    <t>Nomi</t>
+  </si>
+  <si>
+    <t>Ishlab chiqaruvchi</t>
+  </si>
+  <si>
+    <t>Davlat</t>
+  </si>
+  <si>
+    <t>Mening kelish narxim</t>
+  </si>
+  <si>
+    <t>Mening sotish narxim</t>
+  </si>
+  <si>
+    <t>Raqobatdagi nomi</t>
+  </si>
+  <si>
+    <t>Raqobatchi davlati</t>
+  </si>
+  <si>
+    <t>Raqobatchi kelish narxi</t>
+  </si>
+  <si>
+    <t>Raqobatchi sotish narxi</t>
+  </si>
+  <si>
+    <t>Sotish narxi farqi</t>
+  </si>
+  <si>
+    <t>Sotish farqi (%)</t>
+  </si>
+  <si>
+    <t>Raqobatchi (fayl)</t>
+  </si>
+  <si>
+    <t>Paratsetamol 500mg №10</t>
+  </si>
+  <si>
+    <t>Nobel</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Парацетамол таб. 500 мг 10</t>
+  </si>
+  <si>
+    <t>competitor.xlsx</t>
+  </si>
+  <si>
+    <t>Analgin 500mg №10</t>
+  </si>
+  <si>
+    <t>Farmstandart</t>
+  </si>
+  <si>
+    <t>Analgin 500 mg N10</t>
+  </si>
+  <si>
+    <t>Ascorbin kislotasi 100mg</t>
+  </si>
+  <si>
+    <t>Uzfarma</t>
+  </si>
+  <si>
+    <t>Аскорбиновая кислота 100мг</t>
+  </si>
+  <si>
+    <t>Amoksitsillin 500mg №20</t>
+  </si>
+  <si>
+    <t>Sandoz</t>
+  </si>
+  <si>
+    <t>Amoxicillin 500mg #20</t>
+  </si>
+  <si>
+    <t>PricePill — Tahlil Xulosasi</t>
   </si>
   <si>
     <t>Mening price-listim</t>
@@ -24,94 +105,28 @@
     <t>own.xlsx</t>
   </si>
   <si>
-    <t>Sanasi</t>
-  </si>
-  <si>
-    <t>25/05/2026, 20:31:50</t>
-  </si>
-  <si>
-    <t>Jami mahsulotlar</t>
-  </si>
-  <si>
-    <t>Raqobatchida topildi</t>
-  </si>
-  <si>
-    <t>Topilmadi</t>
-  </si>
-  <si>
-    <t>Qimmat sotyapman</t>
-  </si>
-  <si>
-    <t>Arzon sotyapman</t>
-  </si>
-  <si>
-    <t>O'rtacha farq (%)</t>
-  </si>
-  <si>
-    <t>USD kursi (sozlama)</t>
-  </si>
-  <si>
-    <t>№</t>
-  </si>
-  <si>
-    <t>Nomi</t>
-  </si>
-  <si>
-    <t>Ishlab chiqaruvchi</t>
-  </si>
-  <si>
-    <t>Mening narxim</t>
-  </si>
-  <si>
-    <t>Raqobatchi (eng arzon)</t>
-  </si>
-  <si>
-    <t>Raqobatchi fayli</t>
-  </si>
-  <si>
-    <t>Farq (so‘m)</t>
-  </si>
-  <si>
-    <t>Farq (%)</t>
-  </si>
-  <si>
-    <t>Farq ($)</t>
-  </si>
-  <si>
-    <t>Holat</t>
-  </si>
-  <si>
-    <t>Moslik %</t>
-  </si>
-  <si>
-    <t>Analgin 500mg №10</t>
-  </si>
-  <si>
-    <t>Farmstandart</t>
-  </si>
-  <si>
-    <t>competitor.xlsx</t>
-  </si>
-  <si>
-    <t>🔴 Qimmat sotyapsiz</t>
-  </si>
-  <si>
-    <t>Amoksitsillin 500mg №20</t>
-  </si>
-  <si>
-    <t>Sandoz</t>
-  </si>
-  <si>
-    <t>Paratsetamol 500mg №10</t>
-  </si>
-  <si>
-    <t>Nobel</t>
-  </si>
-  <si>
-    <t>Ascorbin kislotasi 100mg</t>
-  </si>
-  <si>
-    <t>Uzfarma</t>
+    <t>Tahlil sanasi</t>
+  </si>
+  <si>
+    <t>01/06/2026, 03:26:24</t>
+  </si>
+  <si>
+    <t>Jami mahsulotlar soni</t>
+  </si>
+  <si>
+    <t>Raqobatchida topilganlari</t>
+  </si>
+  <si>
+    <t>Topilmaganlari</t>
+  </si>
+  <si>
+    <t>Qimmat sotilayotganlari</t>
+  </si>
+  <si>
+    <t>Arzon sotilayotganlari</t>
+  </si>
+  <si>
+    <t>O'rtacha sotish farqi (%)</t>
   </si>
   <si>
     <t>No-shpa 40mg №100</t>
@@ -124,6 +139,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
@@ -134,17 +152,19 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
     </font>
     <font>
       <b/>
+      <color rgb="FF1F497D"/>
+      <sz val="16"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF333333"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -153,7 +173,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F6FED"/>
+        <fgColor rgb="FF1F497D"/>
       </patternFill>
     </fill>
     <fill>
@@ -161,8 +181,23 @@
         <fgColor rgb="FFFCE4E4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F7E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5A5A5A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -170,18 +205,73 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE0E0E0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -521,91 +611,229 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="10" width="27" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
+    <col min="12" max="12" width="23" customWidth="1"/>
+    <col min="13" max="13" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4">
+        <v>4000</v>
+      </c>
+      <c r="F2" s="4">
+        <v>6000</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="4">
+        <v>3800</v>
+      </c>
+      <c r="J2" s="4">
+        <v>5500</v>
+      </c>
+      <c r="K2" s="4">
+        <v>500</v>
+      </c>
+      <c r="L2" s="5">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
+      <c r="B3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="8">
+        <v>3000</v>
+      </c>
+      <c r="F3" s="8">
+        <v>4500</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="8">
+        <v>2900</v>
+      </c>
+      <c r="J3" s="8">
+        <v>5000</v>
+      </c>
+      <c r="K3" s="8">
+        <v>-500</v>
+      </c>
+      <c r="L3" s="9">
+        <v>-0.1</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11">
-        <v>12600</v>
+      <c r="B4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4">
+        <v>1500</v>
+      </c>
+      <c r="F4" s="4">
+        <v>2500</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1400</v>
+      </c>
+      <c r="J4" s="4">
+        <v>2200</v>
+      </c>
+      <c r="K4" s="4">
+        <v>300</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0.13636363636363635</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="4">
+        <v>12000</v>
+      </c>
+      <c r="F5" s="4">
+        <v>18000</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="4">
+        <v>11500</v>
+      </c>
+      <c r="J5" s="4">
+        <v>17000</v>
+      </c>
+      <c r="K5" s="4">
+        <v>1000</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0.0588235294117647</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -613,128 +841,83 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A2:B11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="13">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="4">
-        <v>3000</v>
-      </c>
-      <c r="E2" s="4">
-        <v>2900</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="4">
-        <v>100</v>
-      </c>
-      <c r="H2" s="4">
-        <v>3.4</v>
-      </c>
-      <c r="I2" s="4">
-        <v>0.01</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" s="4">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="4">
-        <v>12000</v>
-      </c>
-      <c r="E3" s="4">
-        <v>11500</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="4">
-        <v>500</v>
-      </c>
-      <c r="H3" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="I3" s="4">
-        <v>0.04</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="4">
-        <v>85</v>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="14">
+        <v>0.046524064171122995</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -742,69 +925,54 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="6" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="3" t="s">
+    <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="16">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="16" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4">
+      <c r="E2" s="13">
         <v>45000</v>
+      </c>
+      <c r="F2" s="13">
+        <v>62000</v>
       </c>
     </row>
   </sheetData>
